--- a/reports/NIFTY_LIVE_Trade_Report.xlsx
+++ b/reports/NIFTY_LIVE_Trade_Report.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Daily!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Monthly!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Trades!$A$1:$L$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Trades!$A$1:$L$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Weekly!$A$1:$E$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Yearly!$A$1:$E$2</definedName>
   </definedNames>
@@ -28,12 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="84">
   <si>
     <t>NIFTY LIVE — Trade &amp; Calendar Report</t>
   </si>
   <si>
-    <t>Live-only rules engine | Strategy SHA-256 2b73c7b13b0ab025… | Phase: SPOT_STRATEGY_ACTIVE</t>
+    <t>Live-only rules engine | Strategy SHA-256 2b73c7b13b0ab025… | Phase: FNO_CLOSE</t>
   </si>
   <si>
     <t>Realized Points</t>
@@ -162,6 +162,9 @@
     <t>(19, 29)/(3, 13)/(5, 10)</t>
   </si>
   <si>
+    <t>FLAT</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -175,9 +178,6 @@
   </si>
   <si>
     <t>Wednesday</t>
-  </si>
-  <si>
-    <t>FLAT</t>
   </si>
   <si>
     <t>Thursday</t>
@@ -858,7 +858,7 @@
         <v>50</v>
       </c>
       <c r="E6" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -1349,9 +1349,47 @@
         <v>34</v>
       </c>
     </row>
+    <row r="11" spans="1:12">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="9">
+        <v>46295.60416666666</v>
+      </c>
+      <c r="F11" s="9">
+        <v>46295.61666666667</v>
+      </c>
+      <c r="G11" s="10">
+        <v>22642.75</v>
+      </c>
+      <c r="H11" s="10">
+        <v>22642.75</v>
+      </c>
+      <c r="I11" s="10">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L10"/>
-  <conditionalFormatting sqref="I2:I10">
+  <autoFilter ref="A1:L11"/>
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -1373,13 +1411,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>25</v>
@@ -1393,7 +1431,7 @@
         <v>46287</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1410,7 +1448,7 @@
         <v>46288</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1419,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1478,7 +1516,7 @@
         <v>46294</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1487,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1495,16 +1533,16 @@
         <v>46295</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="10">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1540,7 +1578,7 @@
         <v>53</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>25</v>
@@ -1574,7 +1612,7 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="10">
         <v>-30</v>
@@ -1616,7 +1654,7 @@
         <v>53</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>25</v>
@@ -1633,7 +1671,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="10">
         <v>-1.25</v>
@@ -1675,7 +1713,7 @@
         <v>53</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>25</v>
@@ -1692,7 +1730,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="10">
         <v>-1.25</v>

--- a/reports/NIFTY_LIVE_Trade_Report.xlsx
+++ b/reports/NIFTY_LIVE_Trade_Report.xlsx
@@ -34,7 +34,7 @@
     <t>Updated IST</t>
   </si>
   <si>
-    <t>2026-10-01 14:33:40</t>
+    <t>2026-10-01 20:08:01</t>
   </si>
   <si>
     <t>Spot</t>
@@ -600,7 +600,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>22331.69921875</v>
+        <v>22421.94921875</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/reports/NIFTY_LIVE_Trade_Report.xlsx
+++ b/reports/NIFTY_LIVE_Trade_Report.xlsx
@@ -34,7 +34,7 @@
     <t>Updated IST</t>
   </si>
   <si>
-    <t>2026-10-01 20:08:01</t>
+    <t>2026-10-01 22:16:03</t>
   </si>
   <si>
     <t>Spot</t>

--- a/reports/NIFTY_LIVE_Trade_Report.xlsx
+++ b/reports/NIFTY_LIVE_Trade_Report.xlsx
@@ -34,7 +34,7 @@
     <t>Updated IST</t>
   </si>
   <si>
-    <t>2026-10-01 22:16:03</t>
+    <t>2026-10-02 15:29:56</t>
   </si>
   <si>
     <t>Spot</t>
@@ -616,7 +616,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/reports/NIFTY_LIVE_Trade_Report.xlsx
+++ b/reports/NIFTY_LIVE_Trade_Report.xlsx
@@ -34,7 +34,7 @@
     <t>Updated IST</t>
   </si>
   <si>
-    <t>2026-10-02 15:29:56</t>
+    <t>2026-10-02 15:54:23</t>
   </si>
   <si>
     <t>Spot</t>

--- a/reports/NIFTY_LIVE_Trade_Report.xlsx
+++ b/reports/NIFTY_LIVE_Trade_Report.xlsx
@@ -34,7 +34,7 @@
     <t>Updated IST</t>
   </si>
   <si>
-    <t>2026-10-02 15:54:23</t>
+    <t>2026-10-02 21:30:22</t>
   </si>
   <si>
     <t>Spot</t>
